--- a/tasks/finalpool/terminal-yf-fetch-gsheet-excel-notion/groundtruth_workspace/Market_Analysis_Report.xlsx
+++ b/tasks/finalpool/terminal-yf-fetch-gsheet-excel-notion/groundtruth_workspace/Market_Analysis_Report.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,23 +28,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -59,9 +49,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -431,27 +420,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Latest_Price</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Return_30d_Pct</t>
         </is>
@@ -474,10 +463,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>200</v>
+        <v>218.94</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2</v>
+        <v>-6.03</v>
       </c>
     </row>
     <row r="3">
@@ -497,10 +486,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>175</v>
+        <v>300.88</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8</v>
+        <v>-9.66</v>
       </c>
     </row>
     <row r="4">
@@ -511,7 +500,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co.</t>
+          <t>JP Morgan Chase &amp; Co.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -520,10 +509,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>240</v>
+        <v>293.55</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1</v>
+        <v>-7.48</v>
       </c>
     </row>
   </sheetData>
@@ -541,17 +530,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Trend</t>
         </is>
@@ -647,22 +636,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>GDP_Correlation</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Inflation_Correlation</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Unemployment_Correlation</t>
         </is>
@@ -749,17 +738,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Rationale</t>
         </is>
@@ -773,12 +762,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Positive 30-day return with consumer confidence at 98.5, above 95 threshold.</t>
+          <t>Negative 30-day return (-6.03%) combined with inflation rate at 3.4%, exceeding the 3.0% threshold.</t>
         </is>
       </c>
     </row>
@@ -790,12 +779,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Positive 30-day return with consumer confidence at 98.5, above 95 threshold.</t>
+          <t>Negative 30-day return (-9.66%) combined with inflation rate at 3.4%, exceeding the 3.0% threshold.</t>
         </is>
       </c>
     </row>
@@ -807,12 +796,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Positive 30-day return with consumer confidence at 98.5, above 95 threshold.</t>
+          <t>Negative 30-day return (-7.48%) combined with inflation rate at 3.4%, exceeding the 3.0% threshold.</t>
         </is>
       </c>
     </row>
